--- a/feb and march posts.xlsx
+++ b/feb and march posts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Desktop\content calendar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93FE7B0B-3545-45F9-9DFC-8B3FF4529434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFD529B-35D3-40CE-9EF2-16A444AC118E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2025" yWindow="3390" windowWidth="35550" windowHeight="15345" xr2:uid="{69224F77-6306-42FB-94AE-B81C5BE972D9}"/>
+    <workbookView xWindow="15" yWindow="4395" windowWidth="38610" windowHeight="15345" xr2:uid="{69224F77-6306-42FB-94AE-B81C5BE972D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="170">
   <si>
     <t>Category</t>
   </si>
@@ -363,6 +363,189 @@
   </si>
   <si>
     <t>Give a gift that puts food on the table and changes lives.\n\nWhen you think of meaningful gifts, consider ones that provide nutrition, income, and hope. Options like chickens, goats, clean water, school supplies, and Bibles spark transformation that lasts for years in families facing extreme challenges.\n\nEvery gift shares the tangible love of Jesus and helps communities overcome poverty with dignity.</t>
+  </si>
+  <si>
+    <t>Org_Impact_Mar3</t>
+  </si>
+  <si>
+    <t>Org_WASH_Mar7</t>
+  </si>
+  <si>
+    <t>Org_Spiritual_Mar11</t>
+  </si>
+  <si>
+    <t>Org_Giving_Mar15</t>
+  </si>
+  <si>
+    <t>When you think of the perfect gift, you may not think of chickens.\n\nBut you might when you hear Betty and Michal’s inspiring story.\n\n“Now we can be sure to eat two meals a day. We have enough money to buy food. My children are healthy,” Betty says. 🙏 \n\nIsn’t that beautiful? \n\nBefore someone caring made room for gifts of love, their family struggled with hunger and uncertainty. Everything changed when someone like you sent chickens and seeds that helped them grow food, earn income and dream again.\n\nYou can help another family put food on the table now and for years to come.\n\nShop the Gift Catalog online &gt; www.fh.org/shop</t>
+  </si>
+  <si>
+    <t>When you give a gift that makes room for love, you help lift families out of extreme poverty and bring real hope to entire communities.\n\nThe Gift Catalog is filled with meaningful ways to share the tangible love of Jesus with children and families facing overwhelming challenges.\n\nFrom goats that help families earn an income to chickens that provide daily nutrition, clean water that saves lives, school supplies that open doors to learning and Bibles that point families to lasting hope… every gift you choose can spark transformation that lasts for years.\n\nBrowse the Gift Catalog today and start giving gifts that change lives. 🎁 fh.org/shop</t>
+  </si>
+  <si>
+    <t>Through a Child's Eyes: Beauty Captured</t>
+  </si>
+  <si>
+    <t>We handed cameras to children and asked them to capture something beautiful in their world.\n\nAbu, age 8, chose to photograph his cow. 💚\n\nHe said “I love my cow very much, because it’s cute and lovely to look at. I love it because it plays with me and it knows my voice. Sometimes I feed my cow and she is comfortable with me.”\n\nThrough Abu’s eyes, we’re reminded that beauty often comes from the simple, loving connections we share every day.</t>
+  </si>
+  <si>
+    <t>https://scontent-mia3-3.xx.fbcdn.net/v/t39.30808-6/574571248_1242965847874930_1292180463714229138_n.jpg?stp=dst-jpg_p526x296_tt6&amp;_nc_cat=108&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=guCnJcbgWgMQ7kNvwEVbxRu&amp;_nc_oc=Adm4Un0CZdr1nQLl8JTP9eWwKvjZFcJRtoewJE5BqKx9JGNNfcCvTToLJdEoMYKUXcY&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-3.xx&amp;_nc_gid=fr5FHjAqOfpZ9g3HQtVfhg&amp;oh=00_Afj5aW-bI8JERqYiZKkQDjpnXuORinnfx7lFiIQhbhM_9Q&amp;oe=69225C75</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid0gDe8pth4pBB81eYQuscPFYGxCu8kCUrX9Xv1bdfZCKkwL1PyEyPSELyzKJm4dUMHl</t>
+  </si>
+  <si>
+    <t>Clap Your Hands All You Nations</t>
+  </si>
+  <si>
+    <t>“Clap your hands, all you nations; shout to God with cries of joy.” \n\n- Psalm 47:1 \n\nThis joyful call to praise reminds us to celebrate God's goodness and faithfulness. In communities around the world, faith brings unity, strength, and reasons to rejoice—even amid challenges. Let's lift our voices in gratitude for His enduring love and provision.</t>
+  </si>
+  <si>
+    <t>https://scontent-dfw5-2.xx.fbcdn.net/v/t39.30808-6/485302908_1059526022952247_547329110755814034_n.jpg?stp=dst-jpg_s960x960_tt6&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=833d8c&amp;_nc_ohc=5_WjUIcbABQQ7kNvwGY2_cA&amp;_nc_oc=AdktH1B1t_Fu_v1dnOVAcRHHFDOagJrUpktqXnabcss4ILfaoxmk0MFkndzyWqbsxJ0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.xx&amp;_nc_gid=y_LRtu6SzHnZbJJuWbucEQ&amp;oh=00_AfnXBCz6yYfyf-UbQ27-C1TIJPdQb75bzLwEWceRlBdwLw&amp;oe=695B1C70</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid02Ldba7ANNTyMs5fhjrycpbKoJhT8F3xqdNBs6beAie4BX8af1c3KtAXtTkmanJ4eTl</t>
+  </si>
+  <si>
+    <t>Joy in Simple Things</t>
+  </si>
+  <si>
+    <t>Happy moments from Blessed Joy in the Philippines! 🇵🇭\n\nBlessed Joy finds joy in family, faith, and traditions. She loves sharing Pancit Palabok and playing Tagu-taguan.\n\nStories like hers show how sponsorship brings hope and cultural pride to children in communities.\n\nThrough faith and community, children like Blessed Joy are thriving and embracing their heritage with confidence.</t>
+  </si>
+  <si>
+    <t>https://scontent-iad3-2.xx.fbcdn.net/v/t39.30808-6/574857026_1247199680784880_8556627046862231935_n.jpg?_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=833d8c&amp;_nc_ohc=ZCKO7ErsC9MQ7kNvwHymVZ-&amp;_nc_oc=AdnQebAeYLsucg0vO8KgC-zIC9FrVOXN5o6NQtH8mUQrahjfkC_ImtzDnt5MyXqkemk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.xx&amp;_nc_gid=O8atAQqnSck8pIl-A1ojGg&amp;oh=00_AfiYXD69aC0LLs9mhp3QhN6oFD4pRwJx75Xyuu3JP-iWgA&amp;oe=69226C7D</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid0SUBt9mye27rWXs1hCAkbZHXYBVj4p8qwxTB4LyYjCKAZ8CJixAEnrzhwhcZxF8v9l</t>
+  </si>
+  <si>
+    <t>Empowering Girls Through Education in Cambodia</t>
+  </si>
+  <si>
+    <t>“I am truly pleased to have access to clean restrooms and menstrual hygiene areas.” — Sreylan, 6th-grade student\n\nIn Rolum Touk, school was uncomfortable for girls due to lack of facilities. Many stayed home during periods, and sickness was common without water.\n\nWith community action, changes came: inclusive latrines, clean water, hygiene education, stocked library, and trained teachers.\n\nNow, girls attend with confidence, focusing on learning and thriving.</t>
+  </si>
+  <si>
+    <t>https://scontent-dfw5-2.xx.fbcdn.net/v/t39.30808-6/559551605_1229192155918966_9010617330290436478_n.jpg?stp=cp6_dst-jpg_s720x720_tt6&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=PUw4wUk_YTAQ7kNvwHBecto&amp;_nc_oc=AdmNnTS0ojrig8Whc_L5drixqiM5ei6bYErNcD38XhygnTrXdeCaPY0xLcpXX60W4M0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw5-2.xx&amp;_nc_gid=3jUeZNbwEmTkbckg1rNuEA&amp;oh=00_AfhHHMTOy5EG_6c45_cTwadVuweV3JvweIxj-OklltQpFg&amp;oe=692244A7</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid0bXhzD1m9LJHLhP1Cf2YM9E3oJx5gmKUUYhkUvwcXgc5tKMzD1AAmudoWa6Bj3kCCl</t>
+  </si>
+  <si>
+    <t>https://relevant-image-url-from-post.jpg</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid0sFB76UnBWJw3LLrrSzuBXf7y9Y6itXbbGAcYvGirJavrngUjtbik6iJ1DXoGD1sdl</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid026qTHca6YKQgFEa4P1FVKngwFo9sJ1QM9xzZadt6GRQ6WmkpT75ZREFKYmdNM2BBgl</t>
+  </si>
+  <si>
+    <t>Org_Giving_Mar22</t>
+  </si>
+  <si>
+    <t>“Clap your hands, all you nations; shout to God with cries of joy.” \n\n- Psalm 47:1 \n\nThis call to joyful praise reminds us to celebrate God's goodness, even in difficult times. In communities worldwide, faith brings unity and strength amid challenges.</t>
+  </si>
+  <si>
+    <t>Org_Spiritual_Mar26</t>
+  </si>
+  <si>
+    <t>Org_Impact_Mar29</t>
+  </si>
+  <si>
+    <t>From Desperation to Nourishment</t>
+  </si>
+  <si>
+    <t>Can you imagine feeding your starving baby only sugar water?\n\nFor one mother, that was reality—until community support provided nutrition, training, and hope. Her child grew healthy, and the family thrived.\n\nStories like this show how care and resources restore lives and build resilience.</t>
+  </si>
+  <si>
+    <t>Org_Impact_Mar11</t>
+  </si>
+  <si>
+    <t>Inspire Kids to Help Other Kids</t>
+  </si>
+  <si>
+    <t>These awesome sisters in Alabama made Christmas decorations and sold them for $5 to send goats, chickens, and clean water from our Gift Catalog to kids in need. \n\nMake room for love like they did—see our Gift Catalog now! FH.org/shop</t>
+  </si>
+  <si>
+    <t>https://scontent-mia3-1.xx.fbcdn.net/v/t51.82787-15/572593645_18531034666016907_9146458639814224479_n.jpg?stp=dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=kGmhXZ1rnMwQ7kNvwEtIzdX&amp;_nc_oc=AdlwIkAfyK1qtTJ0Ne3jg4tPRnhR-ByZtNych7fkVZ6CGN22GcDr0V7A1tgR3uF_sHE&amp;_nc_zt=23&amp;_nc_ht=scontent-mia3-1.xx&amp;_nc_gid=fr5FHjAqOfpZ9g3HQtVfhg&amp;oh=00_Afj-4XoteTAr-4J-RIXwZzSxL9vIBRxvWkzh7W2a3EBPiQ&amp;oe=692245B8</t>
+  </si>
+  <si>
+    <t>See Gift Catalog</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid02ont9ZZhMSdL26tg49vrugUCUyPAVdYj6f6KpZxnc2kNg77prUZ9PhgziFS7fSL9el</t>
+  </si>
+  <si>
+    <t>Org_WASH_Mar15</t>
+  </si>
+  <si>
+    <t>Water Brings Hope to Yvette</t>
+  </si>
+  <si>
+    <t>“Once I spent half my day searching for water. Now, I go to school on time, study without exhaustion, and I dream of becoming a nurse. This water has changed everything in my community.” \n— Yvette, age 10, Rwanda 💚\n\nIn Saruheshyi Cell, clean water was once only a dream. Families walked hours each day to collect water from unsafe sources, and children often missed school. Today, more than 1,000 people have access to safe, reliable water right in their community.\n\nThis transformation was made possible by the leadership of local residents and partners who built and now maintain the system themselves. \n\nClean water doesn’t just fill cups. It fuels education, strengthens health, and restores dignity so that every person can live the life God intended and build a legacy that transforms generations.</t>
+  </si>
+  <si>
+    <t>https://scontent-lax3-1.xx.fbcdn.net/v/t39.30808-6/568273049_1237193248452190_4438941239538307129_n.jpg?stp=cp6_dst-jpg_p843x403_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=gApI6Cpx5W8Q7kNvwGrvKly&amp;_nc_oc=AdnXGfXfpWk0kMmdffuiRlb8977e-deph6XfNQ6R-lxUOyTysskO4RbvY5ZIQ9z8iHY&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.xx&amp;_nc_gid=2aZPtYWGFnHLn5hCDYDSHw&amp;oh=00_AfgHgUOrNAMshf5f3KEZoSU-vbAhBZ54bDPr-n7mZmZW8w&amp;oe=692254BA</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid02Ah7gAQ9sn21jkdHXUQa3Dn9cuPyLXYbCyKqy2PUBaq9zbvdX6UJLJ2AHFTcGrgL9l</t>
+  </si>
+  <si>
+    <t>Hygiene Transforms Lach Lin's Family</t>
+  </si>
+  <si>
+    <t>“My family is not as sick as before because we live with good hygiene. I have the courage from Food for the Hungry staff to share with others, even though I cannot read,” says Lach Lin. 💚\n\nBefore Food for the Hungry entered her community in Cambodia, Lach Lin’s family struggled with many water-related illnesses. “We used to drink from a water tank that did not have a lid and the water did not boil properly, causing family members to experience diarrhea, typhoid fever, and abdominal pain,” she recalls.\n\nThanks to kind supporters like you, Lach Lin and her family now have access to clean water, chickens to raise, and seeds to grow healthy vegetables. These life-changing resources have helped her family live healthier lives and build a brighter future. 💧\n\nThrough your support, families like Lach Lin’s are thriving physically and emotionally, equipped with the tools they need to grow and share hope with others. 🫶🏼</t>
+  </si>
+  <si>
+    <t>https://scontent-mia5-1.xx.fbcdn.net/v/t51.82787-15/568701564_18530207554016907_1436744588319636248_n.jpg?stp=dst-jpg_s720x720_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=m3ZpUDIWKt0Q7kNvwFkhYaJ&amp;_nc_oc=Adkri1-r14iEP-q_LL6zYrx4apGP3w_JR0PRjOGTfwM_LjcaX3UAsMmQQF1grCA-uf0&amp;_nc_zt=23&amp;_nc_ht=scontent-mia5-1.xx&amp;_nc_gid=2aZPtYWGFnHLn5hCDYDSHw&amp;oh=00_AfhrX5vEruiUewgKpR2jiV4INAEhlK-97bSdfGsiLP9FTw&amp;oe=69226552</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid02d3QJZmZ7DjTbBFnXvNAgfs3GzC4SLmTDzjg9Av5FbSV8Ezn2yu6mqAkK5ubMR5VWl</t>
+  </si>
+  <si>
+    <t>Org_WASH_Mar22</t>
+  </si>
+  <si>
+    <t>Water for Edna</t>
+  </si>
+  <si>
+    <t>Will you let a child drink dirty water—or turn on the tap?  💧\n\nIf you’re a child like Edna in Mozambique, you have no choice but to drink dirty, disease-ridden water. And it’s a price no child should have to pay.  \n\n📍According to the World Health Organization, some 1,000 children under the age of 5 die each day because of unsafe water and sanitation. \n\nThat’s 40 kindergarten classes of children just disappearing from planet earth — into eternity — because the water they drink kills them rather than quenches their thirst. \n\nEvery day without clean water puts Edna’s life and future at risk.  \n\nBut your overflowing love today can bring safe, clean water by delivering wells, water tanks, filters and more, before it’s too late. \n\nYour urgent gift means children like Edna can walk a shorter path – just steps from their door – to clean, safe, disease-free water. But she can’t do it without you.   \n\n🙏 And, right now, you can make your donation go 10 times as far to protect lives. \n\nIt means a generous gift of $100 can become $1,000 worth of life-changing clean water. \n\nYour love in action for children like Edna will make 10x more impact, and bring 10x more joy!  \n\nPlease give now and let your love in action be a turning point in a child’s story. There’s no time to waste.   \n\n💚 fh.org/givewateronline</t>
+  </si>
+  <si>
+    <t>https://scontent-lax3-1.xx.fbcdn.net/v/t39.30808-6/564581522_1233497525488429_5161477817722376206_n.jpg?stp=cp6_dst-jpg_s590x590_tt6&amp;_nc_cat=104&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=EXUeUVKDSnYQ7kNvwEXTOUM&amp;_nc_oc=AdmQLW7pkjsABjUsf-rP35E4j28PeNtsLLh8Z03IwqdV9vVSyFhvxmoPsaqAXuT71rE&amp;_nc_zt=23&amp;_nc_ht=scontent-lax3-1.xx&amp;_nc_gid=2aZPtYWGFnHLn5hCDYDSHw&amp;oh=00_Afg5O4y1icixnljetoNcvL1OE1FhshienNKxAEBzomH9Wg&amp;oe=69224D8E</t>
+  </si>
+  <si>
+    <t>Give Now</t>
+  </si>
+  <si>
+    <t>https://fh.org/givewateronline</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid02ZunXXVnoWDZzpjbHt1CEagGPRa4EoP8VaHiACRpHXXHZKWVVS8rWE6w6gHY7716dl</t>
+  </si>
+  <si>
+    <t>Org_Impact_Mar25</t>
+  </si>
+  <si>
+    <t>Empowering People Transforms Communities</t>
+  </si>
+  <si>
+    <t>“When you empower people, they don’t just change their lives, they transform their communities.” 🙌 \n\nIn Mugae, Kenya, what once required a five-hour trek for a single jerry can of water is now just a short walk away. For years, women carried 20-litre cans across harsh terrain, but today, life looks very different.\n\n🚰 Through the work of Food for the Hungry Kenya, the Mugae Maji ya Chumvi borehole was restored with solar power, strong fencing, and sustainable systems that protect this vital water source. \n\n🎉 But the true story of transformation belongs to the people of Mugae themselves. They formed a Borehole Management Committee, elected their own leaders, and now manage the water system with care and vision.\n\n🌳 They are planting trees, cultivating green spaces, and even planning a fishpond to create new sources of income. Clean water is no longer just about survival, it’s about opportunity and dignity.\n\nThis progress is possible because of kind people like you who believe in empowering communities to lead their own change. Together, we’re helping bring water, and hope, closer to home.</t>
+  </si>
+  <si>
+    <t>https://scontent-iad3-2.xx.fbcdn.net/v/t39.30808-6/576392575_1251759230328925_7276332289751622606_n.jpg?stp=dst-jpg_s590x590_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=toHmtR2wkVAQ7kNvwE6bbB4&amp;_nc_oc=AdkLQK-Fe7xQDwEPpgHZpv2H-64oIcstIQzVioCmz7octUD0g7OUQu2MzJ0PsJ7l63U&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.xx&amp;_nc_gid=O8atAQqnSck8pIl-A1ojGg&amp;oh=00_AfhVgF05Mq1HNh3BvQ9aUUGoZLGAjx6FDZ8SxqhvHIKn_Q&amp;oe=69225744</t>
+  </si>
+  <si>
+    <t>Pray for the Philippines</t>
+  </si>
+  <si>
+    <t>💔 Pray with us for the Philippines 🙏\n\nCommunities in the Philippines are facing heartbreaking devastation. After enduring a powerful earthquake just weeks ago, many of the same regions have now been struck by Typhoon Tino (Kalmaegi), bringing heavy rains, flooding, and landslides to areas still struggling to recover.\n\nFamilies have lost homes, livelihoods, and access to clean water. Our hearts ache for those who are suffering and for our brothers and sisters working tirelessly to bring relief.\n\nPlease join us in praying for:\n🙏 Protection and comfort for families displaced by the storm\n🙏 Swift delivery of food, clean water, and shelter\n🙏 Strength and endurance for local responders and churches serving in these communities\n🙏 Hope and peace for all those affected\n\nLord, bring healing and restoration to the Philippines. 🇵🇭</t>
+  </si>
+  <si>
+    <t>https://scontent-iad3-2.xx.fbcdn.net/v/t39.30808-6/578270470_1251759480328900_523223043646446262_n.jpg?stp=dst-jpg_s590x590_tt6&amp;_nc_cat=102&amp;ccb=1-7&amp;_nc_sid=127cfc&amp;_nc_ohc=7sJPeZ8ph1UQ7kNvwH-q3Xc&amp;_nc_oc=AdnZf69vsKRhDUt15T2-pUGt65YG8gkvzV7mjh37hax6Yp6xdjfqCGHZXtxQWoxENpk&amp;_nc_zt=23&amp;_nc_ht=scontent-iad3-2.xx&amp;_nc_gid=O8atAQqnSck8pIl-A1ojGg&amp;oh=00_Afg1S5VjmJnJary1rEIixZxk9PNwRheu347LzbsLMrrzaQ&amp;oe=69224B85</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/foodforthehungry/posts/pfbid03urMb3thzQ7v3Z16dr93cnjkcAkDqUSdPv3xi3Y7CDWJ3Ege2UTYLuJitBHLJKdwl</t>
   </si>
 </sst>
 </file>
@@ -746,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1B81F24-D98A-455E-B9C2-52A23FDC2AC8}">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:X109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -757,6 +940,7 @@
     <col min="7" max="7" width="99.28515625" customWidth="1"/>
     <col min="8" max="8" width="35.28515625" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="13" max="13" width="48.140625" customWidth="1"/>
     <col min="18" max="18" width="127.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2148,6 +2332,3359 @@
       </c>
       <c r="R31" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" t="s">
+        <v>11</v>
+      </c>
+      <c r="M33" t="s">
+        <v>12</v>
+      </c>
+      <c r="N33" t="s">
+        <v>13</v>
+      </c>
+      <c r="O33" t="s">
+        <v>14</v>
+      </c>
+      <c r="P33" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>16</v>
+      </c>
+      <c r="R33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="1">
+        <v>46082</v>
+      </c>
+      <c r="L34" t="s">
+        <v>33</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>26</v>
+      </c>
+      <c r="R34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="1">
+        <v>46084</v>
+      </c>
+      <c r="L35" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>26</v>
+      </c>
+      <c r="R35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="1">
+        <v>46088</v>
+      </c>
+      <c r="L36" t="s">
+        <v>45</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>26</v>
+      </c>
+      <c r="R36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37" t="s">
+        <v>87</v>
+      </c>
+      <c r="H37" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L37" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>26</v>
+      </c>
+      <c r="R37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>63</v>
+      </c>
+      <c r="G38" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="1">
+        <v>46096</v>
+      </c>
+      <c r="L38" t="s">
+        <v>38</v>
+      </c>
+      <c r="M38" t="s">
+        <v>24</v>
+      </c>
+      <c r="N38" t="s">
+        <v>39</v>
+      </c>
+      <c r="O38" t="s">
+        <v>40</v>
+      </c>
+      <c r="P38" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>26</v>
+      </c>
+      <c r="R38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="1">
+        <v>46099</v>
+      </c>
+      <c r="L39" t="s">
+        <v>55</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>26</v>
+      </c>
+      <c r="R39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
+        <v>105</v>
+      </c>
+      <c r="H40" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" s="1">
+        <v>46103</v>
+      </c>
+      <c r="L40" t="s">
+        <v>106</v>
+      </c>
+      <c r="M40" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>26</v>
+      </c>
+      <c r="R40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L41" t="s">
+        <v>38</v>
+      </c>
+      <c r="M41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N41" t="s">
+        <v>39</v>
+      </c>
+      <c r="O41" t="s">
+        <v>40</v>
+      </c>
+      <c r="P41" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>26</v>
+      </c>
+      <c r="R41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" t="s">
+        <v>71</v>
+      </c>
+      <c r="H42" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="1">
+        <v>46110</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>26</v>
+      </c>
+      <c r="R42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" t="s">
+        <v>6</v>
+      </c>
+      <c r="H44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" t="s">
+        <v>10</v>
+      </c>
+      <c r="L44" t="s">
+        <v>11</v>
+      </c>
+      <c r="M44" t="s">
+        <v>12</v>
+      </c>
+      <c r="N44" t="s">
+        <v>13</v>
+      </c>
+      <c r="O44" t="s">
+        <v>14</v>
+      </c>
+      <c r="P44" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>16</v>
+      </c>
+      <c r="R44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="1">
+        <v>46082</v>
+      </c>
+      <c r="L45" t="s">
+        <v>33</v>
+      </c>
+      <c r="M45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" t="s">
+        <v>27</v>
+      </c>
+      <c r="P45" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>26</v>
+      </c>
+      <c r="R45" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>73</v>
+      </c>
+      <c r="G46" t="s">
+        <v>102</v>
+      </c>
+      <c r="H46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="1">
+        <v>46084</v>
+      </c>
+      <c r="L46" t="s">
+        <v>65</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>26</v>
+      </c>
+      <c r="R46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" t="s">
+        <v>43</v>
+      </c>
+      <c r="G47" t="s">
+        <v>97</v>
+      </c>
+      <c r="H47" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="1">
+        <v>46088</v>
+      </c>
+      <c r="L47" t="s">
+        <v>45</v>
+      </c>
+      <c r="M47" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47" t="s">
+        <v>27</v>
+      </c>
+      <c r="P47" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>26</v>
+      </c>
+      <c r="R47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" t="s">
+        <v>115</v>
+      </c>
+      <c r="G48" t="s">
+        <v>116</v>
+      </c>
+      <c r="H48" t="s">
+        <v>24</v>
+      </c>
+      <c r="J48" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L48" t="s">
+        <v>117</v>
+      </c>
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O48" t="s">
+        <v>27</v>
+      </c>
+      <c r="P48" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>26</v>
+      </c>
+      <c r="R48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" t="s">
+        <v>108</v>
+      </c>
+      <c r="H49" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="1">
+        <v>46096</v>
+      </c>
+      <c r="L49" t="s">
+        <v>38</v>
+      </c>
+      <c r="M49" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" t="s">
+        <v>39</v>
+      </c>
+      <c r="O49" t="s">
+        <v>40</v>
+      </c>
+      <c r="P49" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>26</v>
+      </c>
+      <c r="R49" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" t="s">
+        <v>113</v>
+      </c>
+      <c r="H50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50" s="1">
+        <v>46099</v>
+      </c>
+      <c r="L50" t="s">
+        <v>55</v>
+      </c>
+      <c r="M50" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50" t="s">
+        <v>27</v>
+      </c>
+      <c r="P50" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" t="s">
+        <v>104</v>
+      </c>
+      <c r="G51" t="s">
+        <v>105</v>
+      </c>
+      <c r="H51" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" s="1">
+        <v>46103</v>
+      </c>
+      <c r="L51" t="s">
+        <v>106</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" t="s">
+        <v>27</v>
+      </c>
+      <c r="O51" t="s">
+        <v>27</v>
+      </c>
+      <c r="P51" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>26</v>
+      </c>
+      <c r="R51" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" t="s">
+        <v>114</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L52" t="s">
+        <v>38</v>
+      </c>
+      <c r="M52" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" t="s">
+        <v>39</v>
+      </c>
+      <c r="O52" t="s">
+        <v>40</v>
+      </c>
+      <c r="P52" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>26</v>
+      </c>
+      <c r="R52" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" t="s">
+        <v>71</v>
+      </c>
+      <c r="H53" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" s="1">
+        <v>46110</v>
+      </c>
+      <c r="L53" t="s">
+        <v>25</v>
+      </c>
+      <c r="M53" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" t="s">
+        <v>27</v>
+      </c>
+      <c r="O53" t="s">
+        <v>27</v>
+      </c>
+      <c r="P53" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>26</v>
+      </c>
+      <c r="R53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56" t="s">
+        <v>5</v>
+      </c>
+      <c r="G56" t="s">
+        <v>6</v>
+      </c>
+      <c r="H56" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" t="s">
+        <v>8</v>
+      </c>
+      <c r="J56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K56" t="s">
+        <v>10</v>
+      </c>
+      <c r="L56" t="s">
+        <v>11</v>
+      </c>
+      <c r="M56" t="s">
+        <v>12</v>
+      </c>
+      <c r="N56" t="s">
+        <v>13</v>
+      </c>
+      <c r="O56" t="s">
+        <v>14</v>
+      </c>
+      <c r="P56" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>16</v>
+      </c>
+      <c r="R56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H57" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="1">
+        <v>46082</v>
+      </c>
+      <c r="L57" t="s">
+        <v>33</v>
+      </c>
+      <c r="M57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" t="s">
+        <v>27</v>
+      </c>
+      <c r="O57" t="s">
+        <v>27</v>
+      </c>
+      <c r="P57" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>26</v>
+      </c>
+      <c r="R57" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" t="s">
+        <v>109</v>
+      </c>
+      <c r="E58" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" t="s">
+        <v>73</v>
+      </c>
+      <c r="G58" t="s">
+        <v>102</v>
+      </c>
+      <c r="H58" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="1">
+        <v>46084</v>
+      </c>
+      <c r="L58" t="s">
+        <v>65</v>
+      </c>
+      <c r="M58" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" t="s">
+        <v>27</v>
+      </c>
+      <c r="O58" t="s">
+        <v>27</v>
+      </c>
+      <c r="P58" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>26</v>
+      </c>
+      <c r="R58" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" t="s">
+        <v>110</v>
+      </c>
+      <c r="E59" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>43</v>
+      </c>
+      <c r="G59" t="s">
+        <v>97</v>
+      </c>
+      <c r="H59" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" s="1">
+        <v>46088</v>
+      </c>
+      <c r="L59" t="s">
+        <v>45</v>
+      </c>
+      <c r="M59" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" t="s">
+        <v>27</v>
+      </c>
+      <c r="O59" t="s">
+        <v>27</v>
+      </c>
+      <c r="P59" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>26</v>
+      </c>
+      <c r="R59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>111</v>
+      </c>
+      <c r="E60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" t="s">
+        <v>116</v>
+      </c>
+      <c r="H60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L60" t="s">
+        <v>117</v>
+      </c>
+      <c r="M60" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60" t="s">
+        <v>27</v>
+      </c>
+      <c r="P60" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>26</v>
+      </c>
+      <c r="R60" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" t="s">
+        <v>112</v>
+      </c>
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>63</v>
+      </c>
+      <c r="G61" t="s">
+        <v>108</v>
+      </c>
+      <c r="H61" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="1">
+        <v>46096</v>
+      </c>
+      <c r="L61" t="s">
+        <v>38</v>
+      </c>
+      <c r="M61" t="s">
+        <v>24</v>
+      </c>
+      <c r="N61" t="s">
+        <v>39</v>
+      </c>
+      <c r="O61" t="s">
+        <v>40</v>
+      </c>
+      <c r="P61" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>26</v>
+      </c>
+      <c r="R61" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" t="s">
+        <v>52</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" t="s">
+        <v>113</v>
+      </c>
+      <c r="H62" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="1">
+        <v>46099</v>
+      </c>
+      <c r="L62" t="s">
+        <v>55</v>
+      </c>
+      <c r="M62" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" t="s">
+        <v>27</v>
+      </c>
+      <c r="P62" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>26</v>
+      </c>
+      <c r="R62" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" t="s">
+        <v>57</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" t="s">
+        <v>104</v>
+      </c>
+      <c r="G63" t="s">
+        <v>105</v>
+      </c>
+      <c r="H63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J63" s="1">
+        <v>46103</v>
+      </c>
+      <c r="L63" t="s">
+        <v>106</v>
+      </c>
+      <c r="M63" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" t="s">
+        <v>27</v>
+      </c>
+      <c r="O63" t="s">
+        <v>27</v>
+      </c>
+      <c r="P63" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>26</v>
+      </c>
+      <c r="R63" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" t="s">
+        <v>62</v>
+      </c>
+      <c r="E64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" t="s">
+        <v>36</v>
+      </c>
+      <c r="G64" t="s">
+        <v>114</v>
+      </c>
+      <c r="H64" t="s">
+        <v>24</v>
+      </c>
+      <c r="J64" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L64" t="s">
+        <v>38</v>
+      </c>
+      <c r="M64" t="s">
+        <v>24</v>
+      </c>
+      <c r="N64" t="s">
+        <v>39</v>
+      </c>
+      <c r="O64" t="s">
+        <v>40</v>
+      </c>
+      <c r="P64" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>26</v>
+      </c>
+      <c r="R64" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>67</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" t="s">
+        <v>119</v>
+      </c>
+      <c r="G65" t="s">
+        <v>120</v>
+      </c>
+      <c r="H65" t="s">
+        <v>24</v>
+      </c>
+      <c r="J65" s="1">
+        <v>46110</v>
+      </c>
+      <c r="L65" t="s">
+        <v>121</v>
+      </c>
+      <c r="M65" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" t="s">
+        <v>27</v>
+      </c>
+      <c r="O65" t="s">
+        <v>27</v>
+      </c>
+      <c r="P65" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>26</v>
+      </c>
+      <c r="R65" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" t="s">
+        <v>6</v>
+      </c>
+      <c r="H67" t="s">
+        <v>7</v>
+      </c>
+      <c r="I67" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K67" t="s">
+        <v>10</v>
+      </c>
+      <c r="L67" t="s">
+        <v>11</v>
+      </c>
+      <c r="M67" t="s">
+        <v>12</v>
+      </c>
+      <c r="N67" t="s">
+        <v>13</v>
+      </c>
+      <c r="O67" t="s">
+        <v>14</v>
+      </c>
+      <c r="P67" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>16</v>
+      </c>
+      <c r="R67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68" s="1">
+        <v>46082</v>
+      </c>
+      <c r="L68" t="s">
+        <v>33</v>
+      </c>
+      <c r="M68" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" t="s">
+        <v>27</v>
+      </c>
+      <c r="O68" t="s">
+        <v>27</v>
+      </c>
+      <c r="P68" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>26</v>
+      </c>
+      <c r="R68" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" t="s">
+        <v>109</v>
+      </c>
+      <c r="E69" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" t="s">
+        <v>73</v>
+      </c>
+      <c r="G69" t="s">
+        <v>102</v>
+      </c>
+      <c r="H69" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="1">
+        <v>46084</v>
+      </c>
+      <c r="L69" t="s">
+        <v>65</v>
+      </c>
+      <c r="M69" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" t="s">
+        <v>27</v>
+      </c>
+      <c r="O69" t="s">
+        <v>27</v>
+      </c>
+      <c r="P69" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>26</v>
+      </c>
+      <c r="R69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" t="s">
+        <v>110</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" t="s">
+        <v>43</v>
+      </c>
+      <c r="G70" t="s">
+        <v>97</v>
+      </c>
+      <c r="H70" t="s">
+        <v>24</v>
+      </c>
+      <c r="J70" s="1">
+        <v>46088</v>
+      </c>
+      <c r="L70" t="s">
+        <v>45</v>
+      </c>
+      <c r="M70" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" t="s">
+        <v>27</v>
+      </c>
+      <c r="O70" t="s">
+        <v>27</v>
+      </c>
+      <c r="P70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>26</v>
+      </c>
+      <c r="R70" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" t="s">
+        <v>111</v>
+      </c>
+      <c r="E71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" t="s">
+        <v>123</v>
+      </c>
+      <c r="G71" t="s">
+        <v>124</v>
+      </c>
+      <c r="H71" t="s">
+        <v>24</v>
+      </c>
+      <c r="J71" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L71" t="s">
+        <v>125</v>
+      </c>
+      <c r="M71" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" t="s">
+        <v>27</v>
+      </c>
+      <c r="O71" t="s">
+        <v>27</v>
+      </c>
+      <c r="P71" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>26</v>
+      </c>
+      <c r="R71" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" t="s">
+        <v>112</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" t="s">
+        <v>63</v>
+      </c>
+      <c r="G72" t="s">
+        <v>108</v>
+      </c>
+      <c r="H72" t="s">
+        <v>24</v>
+      </c>
+      <c r="J72" s="1">
+        <v>46096</v>
+      </c>
+      <c r="L72" t="s">
+        <v>38</v>
+      </c>
+      <c r="M72" t="s">
+        <v>24</v>
+      </c>
+      <c r="N72" t="s">
+        <v>39</v>
+      </c>
+      <c r="O72" t="s">
+        <v>40</v>
+      </c>
+      <c r="P72" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>26</v>
+      </c>
+      <c r="R72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" t="s">
+        <v>52</v>
+      </c>
+      <c r="E73" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" t="s">
+        <v>53</v>
+      </c>
+      <c r="G73" t="s">
+        <v>113</v>
+      </c>
+      <c r="H73" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" s="1">
+        <v>46099</v>
+      </c>
+      <c r="L73" t="s">
+        <v>55</v>
+      </c>
+      <c r="M73" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" t="s">
+        <v>27</v>
+      </c>
+      <c r="O73" t="s">
+        <v>27</v>
+      </c>
+      <c r="P73" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>26</v>
+      </c>
+      <c r="R73" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" t="s">
+        <v>57</v>
+      </c>
+      <c r="E74" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" t="s">
+        <v>104</v>
+      </c>
+      <c r="G74" t="s">
+        <v>105</v>
+      </c>
+      <c r="H74" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" s="1">
+        <v>46103</v>
+      </c>
+      <c r="L74" t="s">
+        <v>106</v>
+      </c>
+      <c r="M74" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" t="s">
+        <v>27</v>
+      </c>
+      <c r="O74" t="s">
+        <v>27</v>
+      </c>
+      <c r="P74" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>26</v>
+      </c>
+      <c r="R74" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" t="s">
+        <v>62</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
+        <v>36</v>
+      </c>
+      <c r="G75" t="s">
+        <v>114</v>
+      </c>
+      <c r="H75" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L75" t="s">
+        <v>38</v>
+      </c>
+      <c r="M75" t="s">
+        <v>24</v>
+      </c>
+      <c r="N75" t="s">
+        <v>39</v>
+      </c>
+      <c r="O75" t="s">
+        <v>40</v>
+      </c>
+      <c r="P75" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>26</v>
+      </c>
+      <c r="R75" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" t="s">
+        <v>67</v>
+      </c>
+      <c r="E76" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" t="s">
+        <v>123</v>
+      </c>
+      <c r="G76" t="s">
+        <v>124</v>
+      </c>
+      <c r="H76" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="1">
+        <v>46110</v>
+      </c>
+      <c r="L76" t="s">
+        <v>125</v>
+      </c>
+      <c r="M76" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" t="s">
+        <v>27</v>
+      </c>
+      <c r="O76" t="s">
+        <v>27</v>
+      </c>
+      <c r="P76" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>26</v>
+      </c>
+      <c r="R76" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" t="s">
+        <v>3</v>
+      </c>
+      <c r="E78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" t="s">
+        <v>5</v>
+      </c>
+      <c r="G78" t="s">
+        <v>6</v>
+      </c>
+      <c r="H78" t="s">
+        <v>7</v>
+      </c>
+      <c r="I78" t="s">
+        <v>8</v>
+      </c>
+      <c r="J78" t="s">
+        <v>9</v>
+      </c>
+      <c r="K78" t="s">
+        <v>10</v>
+      </c>
+      <c r="L78" t="s">
+        <v>11</v>
+      </c>
+      <c r="M78" t="s">
+        <v>12</v>
+      </c>
+      <c r="N78" t="s">
+        <v>13</v>
+      </c>
+      <c r="O78" t="s">
+        <v>14</v>
+      </c>
+      <c r="P78" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>16</v>
+      </c>
+      <c r="R78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" t="s">
+        <v>32</v>
+      </c>
+      <c r="H79" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" s="1">
+        <v>46082</v>
+      </c>
+      <c r="L79" t="s">
+        <v>33</v>
+      </c>
+      <c r="M79" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" t="s">
+        <v>27</v>
+      </c>
+      <c r="O79" t="s">
+        <v>27</v>
+      </c>
+      <c r="P79" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>26</v>
+      </c>
+      <c r="R79" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" t="s">
+        <v>73</v>
+      </c>
+      <c r="G80" t="s">
+        <v>102</v>
+      </c>
+      <c r="H80" t="s">
+        <v>24</v>
+      </c>
+      <c r="J80" s="1">
+        <v>46084</v>
+      </c>
+      <c r="L80" t="s">
+        <v>65</v>
+      </c>
+      <c r="M80" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" t="s">
+        <v>27</v>
+      </c>
+      <c r="O80" t="s">
+        <v>27</v>
+      </c>
+      <c r="P80" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>26</v>
+      </c>
+      <c r="R80" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" t="s">
+        <v>110</v>
+      </c>
+      <c r="E81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F81" t="s">
+        <v>43</v>
+      </c>
+      <c r="G81" t="s">
+        <v>97</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
+      </c>
+      <c r="J81" s="1">
+        <v>46088</v>
+      </c>
+      <c r="L81" t="s">
+        <v>45</v>
+      </c>
+      <c r="M81" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" t="s">
+        <v>27</v>
+      </c>
+      <c r="O81" t="s">
+        <v>27</v>
+      </c>
+      <c r="P81" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>26</v>
+      </c>
+      <c r="R81" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" t="s">
+        <v>111</v>
+      </c>
+      <c r="E82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F82" t="s">
+        <v>127</v>
+      </c>
+      <c r="G82" t="s">
+        <v>128</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L82" t="s">
+        <v>129</v>
+      </c>
+      <c r="M82" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" t="s">
+        <v>27</v>
+      </c>
+      <c r="O82" t="s">
+        <v>27</v>
+      </c>
+      <c r="P82" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>26</v>
+      </c>
+      <c r="R82" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" t="s">
+        <v>112</v>
+      </c>
+      <c r="E83" t="s">
+        <v>21</v>
+      </c>
+      <c r="F83" t="s">
+        <v>63</v>
+      </c>
+      <c r="G83" t="s">
+        <v>108</v>
+      </c>
+      <c r="H83" t="s">
+        <v>24</v>
+      </c>
+      <c r="J83" s="1">
+        <v>46096</v>
+      </c>
+      <c r="L83" t="s">
+        <v>38</v>
+      </c>
+      <c r="M83" t="s">
+        <v>24</v>
+      </c>
+      <c r="N83" t="s">
+        <v>39</v>
+      </c>
+      <c r="O83" t="s">
+        <v>40</v>
+      </c>
+      <c r="P83" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>26</v>
+      </c>
+      <c r="R83" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" t="s">
+        <v>21</v>
+      </c>
+      <c r="F84" t="s">
+        <v>53</v>
+      </c>
+      <c r="G84" t="s">
+        <v>113</v>
+      </c>
+      <c r="H84" t="s">
+        <v>24</v>
+      </c>
+      <c r="J84" s="1">
+        <v>46099</v>
+      </c>
+      <c r="L84" t="s">
+        <v>55</v>
+      </c>
+      <c r="M84" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" t="s">
+        <v>27</v>
+      </c>
+      <c r="O84" t="s">
+        <v>27</v>
+      </c>
+      <c r="P84" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>26</v>
+      </c>
+      <c r="R84" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" t="s">
+        <v>57</v>
+      </c>
+      <c r="E85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F85" t="s">
+        <v>104</v>
+      </c>
+      <c r="G85" t="s">
+        <v>105</v>
+      </c>
+      <c r="H85" t="s">
+        <v>24</v>
+      </c>
+      <c r="J85" s="1">
+        <v>46103</v>
+      </c>
+      <c r="L85" t="s">
+        <v>106</v>
+      </c>
+      <c r="M85" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" t="s">
+        <v>27</v>
+      </c>
+      <c r="O85" t="s">
+        <v>27</v>
+      </c>
+      <c r="P85" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>26</v>
+      </c>
+      <c r="R85" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" t="s">
+        <v>62</v>
+      </c>
+      <c r="E86" t="s">
+        <v>21</v>
+      </c>
+      <c r="F86" t="s">
+        <v>36</v>
+      </c>
+      <c r="G86" t="s">
+        <v>114</v>
+      </c>
+      <c r="H86" t="s">
+        <v>24</v>
+      </c>
+      <c r="J86" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L86" t="s">
+        <v>38</v>
+      </c>
+      <c r="M86" t="s">
+        <v>24</v>
+      </c>
+      <c r="N86" t="s">
+        <v>39</v>
+      </c>
+      <c r="O86" t="s">
+        <v>40</v>
+      </c>
+      <c r="P86" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>26</v>
+      </c>
+      <c r="R86" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" t="s">
+        <v>67</v>
+      </c>
+      <c r="E87" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87" t="s">
+        <v>123</v>
+      </c>
+      <c r="G87" t="s">
+        <v>124</v>
+      </c>
+      <c r="H87" t="s">
+        <v>24</v>
+      </c>
+      <c r="J87" s="1">
+        <v>46110</v>
+      </c>
+      <c r="L87" t="s">
+        <v>125</v>
+      </c>
+      <c r="M87" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" t="s">
+        <v>27</v>
+      </c>
+      <c r="O87" t="s">
+        <v>27</v>
+      </c>
+      <c r="P87" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>26</v>
+      </c>
+      <c r="R87" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" t="s">
+        <v>6</v>
+      </c>
+      <c r="H89" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" t="s">
+        <v>9</v>
+      </c>
+      <c r="K89" t="s">
+        <v>10</v>
+      </c>
+      <c r="L89" t="s">
+        <v>11</v>
+      </c>
+      <c r="M89" t="s">
+        <v>12</v>
+      </c>
+      <c r="N89" t="s">
+        <v>13</v>
+      </c>
+      <c r="O89" t="s">
+        <v>14</v>
+      </c>
+      <c r="P89" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>16</v>
+      </c>
+      <c r="R89" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" t="s">
+        <v>140</v>
+      </c>
+      <c r="E90" t="s">
+        <v>21</v>
+      </c>
+      <c r="F90" t="s">
+        <v>141</v>
+      </c>
+      <c r="G90" t="s">
+        <v>142</v>
+      </c>
+      <c r="H90" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L90" t="s">
+        <v>143</v>
+      </c>
+      <c r="M90" t="s">
+        <v>24</v>
+      </c>
+      <c r="N90" t="s">
+        <v>144</v>
+      </c>
+      <c r="O90" t="s">
+        <v>40</v>
+      </c>
+      <c r="P90" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>26</v>
+      </c>
+      <c r="R90" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D91" t="s">
+        <v>146</v>
+      </c>
+      <c r="E91" t="s">
+        <v>21</v>
+      </c>
+      <c r="F91" t="s">
+        <v>147</v>
+      </c>
+      <c r="G91" t="s">
+        <v>148</v>
+      </c>
+      <c r="H91" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="1">
+        <v>46096</v>
+      </c>
+      <c r="L91" t="s">
+        <v>149</v>
+      </c>
+      <c r="M91" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" t="s">
+        <v>27</v>
+      </c>
+      <c r="O91" t="s">
+        <v>27</v>
+      </c>
+      <c r="P91" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>26</v>
+      </c>
+      <c r="R91" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" t="s">
+        <v>29</v>
+      </c>
+      <c r="D92" t="s">
+        <v>52</v>
+      </c>
+      <c r="E92" t="s">
+        <v>21</v>
+      </c>
+      <c r="F92" t="s">
+        <v>151</v>
+      </c>
+      <c r="G92" t="s">
+        <v>152</v>
+      </c>
+      <c r="H92" t="s">
+        <v>24</v>
+      </c>
+      <c r="J92" s="1">
+        <v>46099</v>
+      </c>
+      <c r="L92" t="s">
+        <v>153</v>
+      </c>
+      <c r="M92" t="s">
+        <v>26</v>
+      </c>
+      <c r="N92" t="s">
+        <v>27</v>
+      </c>
+      <c r="O92" t="s">
+        <v>27</v>
+      </c>
+      <c r="P92" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>26</v>
+      </c>
+      <c r="R92" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" t="s">
+        <v>29</v>
+      </c>
+      <c r="D93" t="s">
+        <v>155</v>
+      </c>
+      <c r="E93" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" t="s">
+        <v>156</v>
+      </c>
+      <c r="G93" t="s">
+        <v>157</v>
+      </c>
+      <c r="H93" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" s="1">
+        <v>46103</v>
+      </c>
+      <c r="L93" t="s">
+        <v>158</v>
+      </c>
+      <c r="M93" t="s">
+        <v>24</v>
+      </c>
+      <c r="N93" t="s">
+        <v>159</v>
+      </c>
+      <c r="O93" t="s">
+        <v>160</v>
+      </c>
+      <c r="P93" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>26</v>
+      </c>
+      <c r="R93" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" t="s">
+        <v>162</v>
+      </c>
+      <c r="E94" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" t="s">
+        <v>163</v>
+      </c>
+      <c r="G94" t="s">
+        <v>164</v>
+      </c>
+      <c r="H94" t="s">
+        <v>24</v>
+      </c>
+      <c r="J94" s="1">
+        <v>46106</v>
+      </c>
+      <c r="L94" t="s">
+        <v>165</v>
+      </c>
+      <c r="M94" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" t="s">
+        <v>27</v>
+      </c>
+      <c r="O94" t="s">
+        <v>27</v>
+      </c>
+      <c r="P94" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>26</v>
+      </c>
+      <c r="R94" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" t="s">
+        <v>67</v>
+      </c>
+      <c r="E95" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95" t="s">
+        <v>166</v>
+      </c>
+      <c r="G95" t="s">
+        <v>167</v>
+      </c>
+      <c r="H95" t="s">
+        <v>24</v>
+      </c>
+      <c r="J95" s="1">
+        <v>46110</v>
+      </c>
+      <c r="L95" t="s">
+        <v>168</v>
+      </c>
+      <c r="M95" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" t="s">
+        <v>27</v>
+      </c>
+      <c r="O95" t="s">
+        <v>27</v>
+      </c>
+      <c r="P95" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>26</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" t="s">
+        <v>134</v>
+      </c>
+      <c r="E96" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" t="s">
+        <v>119</v>
+      </c>
+      <c r="G96" t="s">
+        <v>135</v>
+      </c>
+      <c r="H96" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="1">
+        <v>46103</v>
+      </c>
+      <c r="L96" t="s">
+        <v>50</v>
+      </c>
+      <c r="M96" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" t="s">
+        <v>27</v>
+      </c>
+      <c r="O96" t="s">
+        <v>27</v>
+      </c>
+      <c r="P96" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>26</v>
+      </c>
+      <c r="R96" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" t="s">
+        <v>136</v>
+      </c>
+      <c r="E97" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" t="s">
+        <v>123</v>
+      </c>
+      <c r="G97" t="s">
+        <v>124</v>
+      </c>
+      <c r="H97" t="s">
+        <v>24</v>
+      </c>
+      <c r="J97" s="1">
+        <v>46107</v>
+      </c>
+      <c r="L97" t="s">
+        <v>125</v>
+      </c>
+      <c r="M97" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" t="s">
+        <v>27</v>
+      </c>
+      <c r="O97" t="s">
+        <v>27</v>
+      </c>
+      <c r="P97" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>26</v>
+      </c>
+      <c r="R97" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" t="s">
+        <v>137</v>
+      </c>
+      <c r="E98" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" t="s">
+        <v>138</v>
+      </c>
+      <c r="G98" t="s">
+        <v>139</v>
+      </c>
+      <c r="H98" t="s">
+        <v>24</v>
+      </c>
+      <c r="J98" s="1">
+        <v>46110</v>
+      </c>
+      <c r="L98" t="s">
+        <v>131</v>
+      </c>
+      <c r="M98" t="s">
+        <v>26</v>
+      </c>
+      <c r="N98" t="s">
+        <v>27</v>
+      </c>
+      <c r="O98" t="s">
+        <v>27</v>
+      </c>
+      <c r="P98" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>26</v>
+      </c>
+      <c r="R98" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G100" t="s">
+        <v>0</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1</v>
+      </c>
+      <c r="I100" t="s">
+        <v>2</v>
+      </c>
+      <c r="J100" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" t="s">
+        <v>6</v>
+      </c>
+      <c r="N100" t="s">
+        <v>7</v>
+      </c>
+      <c r="O100" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>10</v>
+      </c>
+      <c r="R100" t="s">
+        <v>11</v>
+      </c>
+      <c r="S100" t="s">
+        <v>12</v>
+      </c>
+      <c r="T100" t="s">
+        <v>13</v>
+      </c>
+      <c r="U100" t="s">
+        <v>14</v>
+      </c>
+      <c r="V100" t="s">
+        <v>15</v>
+      </c>
+      <c r="W100" t="s">
+        <v>16</v>
+      </c>
+      <c r="X100" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s">
+        <v>20</v>
+      </c>
+      <c r="K101" t="s">
+        <v>21</v>
+      </c>
+      <c r="L101" t="s">
+        <v>31</v>
+      </c>
+      <c r="M101" t="s">
+        <v>32</v>
+      </c>
+      <c r="N101" t="s">
+        <v>24</v>
+      </c>
+      <c r="P101" s="1">
+        <v>46082</v>
+      </c>
+      <c r="R101" t="s">
+        <v>33</v>
+      </c>
+      <c r="S101" t="s">
+        <v>26</v>
+      </c>
+      <c r="T101" t="s">
+        <v>27</v>
+      </c>
+      <c r="U101" t="s">
+        <v>27</v>
+      </c>
+      <c r="V101" t="s">
+        <v>26</v>
+      </c>
+      <c r="W101" t="s">
+        <v>26</v>
+      </c>
+      <c r="X101" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>29</v>
+      </c>
+      <c r="J102" t="s">
+        <v>109</v>
+      </c>
+      <c r="K102" t="s">
+        <v>21</v>
+      </c>
+      <c r="L102" t="s">
+        <v>73</v>
+      </c>
+      <c r="M102" t="s">
+        <v>102</v>
+      </c>
+      <c r="N102" t="s">
+        <v>24</v>
+      </c>
+      <c r="P102" s="1">
+        <v>46084</v>
+      </c>
+      <c r="R102" t="s">
+        <v>65</v>
+      </c>
+      <c r="S102" t="s">
+        <v>26</v>
+      </c>
+      <c r="T102" t="s">
+        <v>27</v>
+      </c>
+      <c r="U102" t="s">
+        <v>27</v>
+      </c>
+      <c r="V102" t="s">
+        <v>26</v>
+      </c>
+      <c r="W102" t="s">
+        <v>26</v>
+      </c>
+      <c r="X102" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>29</v>
+      </c>
+      <c r="J103" t="s">
+        <v>110</v>
+      </c>
+      <c r="K103" t="s">
+        <v>21</v>
+      </c>
+      <c r="L103" t="s">
+        <v>43</v>
+      </c>
+      <c r="M103" t="s">
+        <v>97</v>
+      </c>
+      <c r="N103" t="s">
+        <v>24</v>
+      </c>
+      <c r="P103" s="1">
+        <v>46088</v>
+      </c>
+      <c r="R103" t="s">
+        <v>45</v>
+      </c>
+      <c r="S103" t="s">
+        <v>26</v>
+      </c>
+      <c r="T103" t="s">
+        <v>27</v>
+      </c>
+      <c r="U103" t="s">
+        <v>27</v>
+      </c>
+      <c r="V103" t="s">
+        <v>26</v>
+      </c>
+      <c r="W103" t="s">
+        <v>26</v>
+      </c>
+      <c r="X103" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s">
+        <v>111</v>
+      </c>
+      <c r="K104" t="s">
+        <v>21</v>
+      </c>
+      <c r="L104" t="s">
+        <v>115</v>
+      </c>
+      <c r="M104" t="s">
+        <v>116</v>
+      </c>
+      <c r="N104" t="s">
+        <v>24</v>
+      </c>
+      <c r="P104" s="1">
+        <v>46092</v>
+      </c>
+      <c r="R104" t="s">
+        <v>117</v>
+      </c>
+      <c r="S104" t="s">
+        <v>26</v>
+      </c>
+      <c r="T104" t="s">
+        <v>27</v>
+      </c>
+      <c r="U104" t="s">
+        <v>27</v>
+      </c>
+      <c r="V104" t="s">
+        <v>26</v>
+      </c>
+      <c r="W104" t="s">
+        <v>26</v>
+      </c>
+      <c r="X104" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>29</v>
+      </c>
+      <c r="J105" t="s">
+        <v>112</v>
+      </c>
+      <c r="K105" t="s">
+        <v>21</v>
+      </c>
+      <c r="L105" t="s">
+        <v>63</v>
+      </c>
+      <c r="M105" t="s">
+        <v>108</v>
+      </c>
+      <c r="N105" t="s">
+        <v>24</v>
+      </c>
+      <c r="P105" s="1">
+        <v>46096</v>
+      </c>
+      <c r="R105" t="s">
+        <v>38</v>
+      </c>
+      <c r="S105" t="s">
+        <v>24</v>
+      </c>
+      <c r="T105" t="s">
+        <v>39</v>
+      </c>
+      <c r="U105" t="s">
+        <v>40</v>
+      </c>
+      <c r="V105" t="s">
+        <v>26</v>
+      </c>
+      <c r="W105" t="s">
+        <v>26</v>
+      </c>
+      <c r="X105" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>29</v>
+      </c>
+      <c r="J106" t="s">
+        <v>52</v>
+      </c>
+      <c r="K106" t="s">
+        <v>21</v>
+      </c>
+      <c r="L106" t="s">
+        <v>53</v>
+      </c>
+      <c r="M106" t="s">
+        <v>113</v>
+      </c>
+      <c r="N106" t="s">
+        <v>24</v>
+      </c>
+      <c r="P106" s="1">
+        <v>46099</v>
+      </c>
+      <c r="R106" t="s">
+        <v>55</v>
+      </c>
+      <c r="S106" t="s">
+        <v>26</v>
+      </c>
+      <c r="T106" t="s">
+        <v>27</v>
+      </c>
+      <c r="U106" t="s">
+        <v>27</v>
+      </c>
+      <c r="V106" t="s">
+        <v>26</v>
+      </c>
+      <c r="W106" t="s">
+        <v>26</v>
+      </c>
+      <c r="X106" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s">
+        <v>29</v>
+      </c>
+      <c r="J107" t="s">
+        <v>57</v>
+      </c>
+      <c r="K107" t="s">
+        <v>21</v>
+      </c>
+      <c r="L107" t="s">
+        <v>104</v>
+      </c>
+      <c r="M107" t="s">
+        <v>105</v>
+      </c>
+      <c r="N107" t="s">
+        <v>24</v>
+      </c>
+      <c r="P107" s="1">
+        <v>46103</v>
+      </c>
+      <c r="R107" t="s">
+        <v>106</v>
+      </c>
+      <c r="S107" t="s">
+        <v>26</v>
+      </c>
+      <c r="T107" t="s">
+        <v>27</v>
+      </c>
+      <c r="U107" t="s">
+        <v>27</v>
+      </c>
+      <c r="V107" t="s">
+        <v>26</v>
+      </c>
+      <c r="W107" t="s">
+        <v>26</v>
+      </c>
+      <c r="X107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>29</v>
+      </c>
+      <c r="J108" t="s">
+        <v>62</v>
+      </c>
+      <c r="K108" t="s">
+        <v>21</v>
+      </c>
+      <c r="L108" t="s">
+        <v>36</v>
+      </c>
+      <c r="M108" t="s">
+        <v>114</v>
+      </c>
+      <c r="N108" t="s">
+        <v>24</v>
+      </c>
+      <c r="P108" s="1">
+        <v>46106</v>
+      </c>
+      <c r="R108" t="s">
+        <v>38</v>
+      </c>
+      <c r="S108" t="s">
+        <v>24</v>
+      </c>
+      <c r="T108" t="s">
+        <v>39</v>
+      </c>
+      <c r="U108" t="s">
+        <v>40</v>
+      </c>
+      <c r="V108" t="s">
+        <v>26</v>
+      </c>
+      <c r="W108" t="s">
+        <v>26</v>
+      </c>
+      <c r="X108" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+      <c r="J109" t="s">
+        <v>67</v>
+      </c>
+      <c r="K109" t="s">
+        <v>21</v>
+      </c>
+      <c r="L109" t="s">
+        <v>123</v>
+      </c>
+      <c r="M109" t="s">
+        <v>124</v>
+      </c>
+      <c r="N109" t="s">
+        <v>24</v>
+      </c>
+      <c r="P109" s="1">
+        <v>46110</v>
+      </c>
+      <c r="R109" t="s">
+        <v>125</v>
+      </c>
+      <c r="S109" t="s">
+        <v>26</v>
+      </c>
+      <c r="T109" t="s">
+        <v>27</v>
+      </c>
+      <c r="U109" t="s">
+        <v>27</v>
+      </c>
+      <c r="V109" t="s">
+        <v>26</v>
+      </c>
+      <c r="W109" t="s">
+        <v>26</v>
+      </c>
+      <c r="X109" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2170,6 +5707,7 @@
     <hyperlink ref="R19" r:id="rId16" xr:uid="{1041A874-51BA-4FEB-8A6D-9F7983CD4775}"/>
     <hyperlink ref="R20" r:id="rId17" xr:uid="{1A8038B8-2CF1-41FE-A6C0-623CCDE1ADAC}"/>
     <hyperlink ref="R21" r:id="rId18" xr:uid="{8B357D3B-49BA-401A-B211-973449F7936E}"/>
+    <hyperlink ref="R95" r:id="rId19" xr:uid="{F271F129-BF6F-4E81-ABDF-197101B18D02}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
